--- a/r4-ELGA-IV-Diabetes-main/StructureDefinition-diab-composition.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/StructureDefinition-diab-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T13:11:58+00:00</t>
+    <t>2025-02-28T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-main/StructureDefinition-diab-composition.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/StructureDefinition-diab-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T14:02:02+00:00</t>
+    <t>2025-03-03T10:25:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
